--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1,299 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>value_type</t>
-  </si>
-  <si>
-    <t>read_schema_from_file</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>mode</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>output</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>记录类名</t>
-  </si>
-  <si>
-    <t>从excel读取定义</t>
-  </si>
-  <si>
-    <t>文件列表</t>
-  </si>
-  <si>
-    <t>表id字段</t>
-  </si>
-  <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>输出文件名</t>
-  </si>
-  <si>
-    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
-  </si>
-  <si>
-    <t>可以多个，以逗号','分隔</t>
-  </si>
-  <si>
-    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
-  </si>
-  <si>
-    <t>取值one|map|list，为空自动为map</t>
-  </si>
-  <si>
-    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
-  </si>
-  <si>
-    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>UI.TbUIFormConfig</t>
-  </si>
-  <si>
-    <t>UIFormConfig</t>
-  </si>
-  <si>
-    <t>界面UI.xlsx</t>
-  </si>
-  <si>
-    <t>Entity.TbEntityConfig</t>
-  </si>
-  <si>
-    <t>EntityConfig</t>
-  </si>
-  <si>
-    <t>实体.xlsx</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -599,170 +477,168 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -816,11 +692,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1080,139 +1019,420 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.575" customWidth="1"/>
-    <col min="4" max="4" width="32.425" customWidth="1"/>
-    <col min="5" max="5" width="24.3833333333333" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col width="5.91666666666667" customWidth="1" style="4" min="1" max="1"/>
+    <col width="29" customWidth="1" style="4" min="2" max="2"/>
+    <col width="19.0833333333333" customWidth="1" style="4" min="3" max="3"/>
+    <col width="53.0833333333333" customWidth="1" style="4" min="4" max="4"/>
+    <col width="22.6666666666667" customWidth="1" style="4" min="5" max="5"/>
+    <col width="89.25" customWidth="1" style="4" min="6" max="6"/>
+    <col width="31.5" customWidth="1" style="4" min="7" max="7"/>
+    <col width="56.75" customWidth="1" style="4" min="8" max="8"/>
+    <col width="9" customWidth="1" style="4" min="9" max="9"/>
+    <col width="4.75" customWidth="1" style="4" min="10" max="10"/>
+    <col width="33" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" customFormat="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>read_schema_from_file</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" customFormat="1" s="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>记录类名</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>从excel读取定义</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>文件列表</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>表id字段</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>输出文件名</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>可以多个，以逗号','分隔</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>取值one|map|list，为空自动为map</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" customFormat="1" s="2">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UI.TbUIFormConfig</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UIFormConfig</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>界面UI.xlsx</t>
+        </is>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
+    <row r="5" customFormat="1" s="3">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Entity.TbEntityConfig</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EntityConfig</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>实体.xlsx</t>
+        </is>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hero.TbHeroConfig</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HeroConfig</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HeroConfig.xlsx</t>
+        </is>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:11">
-      <c r="B4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="2" t="b">
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hero.TbHeroAttackConfig</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HeroAttackConfig</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>29</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HeroAttackConfig.xlsx</t>
+        </is>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:11">
-      <c r="B5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="3" t="b">
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hero.TbHeroLevelConfig</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HeroLevelConfig</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>32</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HeroLevelConfig.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Monster.TbMonsterConfig</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MonsterConfig</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MonsterConfig.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Monster.TbMonsterAttackConfig</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MonsterAttackConfig</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MonsterAttackConfig.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Battle.TbAttackConfig</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AttackConfig</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AttackConfig.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Battle.TbBattleConfig</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BattleConfig</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BattleConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Level.TbLevelConfig</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LevelConfig</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LevelConfig.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Level.TbLevelWaveConfig</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LevelWaveConfig</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LevelWaveConfig.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Level.TbLevelSpawnConfig</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LevelSpawnConfig</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LevelSpawnConfig.xlsx</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="5.91666666666667" customWidth="1" style="4" min="1" max="1"/>
@@ -1249,12 +1249,12 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hero.TbHeroAttackConfig</t>
+          <t>Hero.TbHeroLevelConfig</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HeroAttackConfig</t>
+          <t>HeroLevelConfig</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -1262,19 +1262,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HeroAttackConfig.xlsx</t>
+          <t>HeroLevelConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hero.TbHeroLevelConfig</t>
+          <t>Monster.TbMonsterConfig</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HeroLevelConfig</t>
+          <t>MonsterConfig</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -1282,19 +1282,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HeroLevelConfig.xlsx</t>
+          <t>MonsterConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Monster.TbMonsterConfig</t>
+          <t>Battle.TbAttackConfig</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MonsterConfig</t>
+          <t>AttackConfig</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -1302,19 +1302,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MonsterConfig.xlsx</t>
+          <t>AttackConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Monster.TbMonsterAttackConfig</t>
+          <t>Battle.TbBattleConfig</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MonsterAttackConfig</t>
+          <t>BattleConfig</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1322,19 +1322,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MonsterAttackConfig.xlsx</t>
+          <t>BattleConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Battle.TbAttackConfig</t>
+          <t>Level.TbLevelConfig</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AttackConfig</t>
+          <t>LevelConfig</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -1342,19 +1347,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AttackConfig.xlsx</t>
+          <t>LevelConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Battle.TbBattleConfig</t>
+          <t>Level.TbLevelWaveConfig</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BattleConfig</t>
+          <t>LevelWaveConfig</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -1362,24 +1367,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BattleConfig.xlsx</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>one</t>
+          <t>LevelWaveConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Level.TbLevelConfig</t>
+          <t>Level.TbLevelSpawnConfig</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LevelConfig</t>
+          <t>LevelSpawnConfig</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -1387,19 +1387,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LevelConfig.xlsx</t>
+          <t>LevelSpawnConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Level.TbLevelWaveConfig</t>
+          <t>Sound.TbSoundConfig</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LevelWaveConfig</t>
+          <t>SoundConfig</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -1407,27 +1407,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LevelWaveConfig.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Level.TbLevelSpawnConfig</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LevelSpawnConfig</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LevelSpawnConfig.xlsx</t>
+          <t>SoundConfig.xlsx</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="5.91666666666667" customWidth="1" style="4" min="1" max="1"/>
@@ -1334,78 +1334,18 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Level.TbLevelConfig</t>
+          <t>Sound.TbSoundConfig</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LevelConfig</t>
+          <t>SoundConfig</t>
         </is>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>LevelConfig.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Level.TbLevelWaveConfig</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LevelWaveConfig</t>
-        </is>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LevelWaveConfig.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Level.TbLevelSpawnConfig</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LevelSpawnConfig</t>
-        </is>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LevelSpawnConfig.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Sound.TbSoundConfig</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SoundConfig</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>SoundConfig.xlsx</t>
         </is>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="5.91666666666667" customWidth="1" style="4" min="1" max="1"/>
@@ -1187,167 +1187,212 @@
       </c>
     </row>
     <row r="4" customFormat="1" s="2">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>UI.TbUIFormConfig</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>UIFormConfig</t>
         </is>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>界面UI.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" customFormat="1" s="3">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Entity.TbEntityConfig</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>EntityConfig</t>
         </is>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>实体.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Hero.TbHeroConfig</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>HeroConfig</t>
         </is>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>HeroConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Hero.TbHeroLevelConfig</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>HeroLevelConfig</t>
         </is>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>HeroLevelConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Monster.TbMonsterConfig</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>MonsterConfig</t>
         </is>
       </c>
-      <c r="D8" t="b">
+      <c r="D8" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>MonsterConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Battle.TbAttackConfig</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>AttackConfig</t>
         </is>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>AttackConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Battle.TbBattleConfig</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>BattleConfig</t>
         </is>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>BattleConfig.xlsx</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Sound.TbSoundConfig</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>SoundConfig</t>
         </is>
       </c>
-      <c r="D11" t="b">
+      <c r="D11" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>SoundConfig.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Level.TbLevelConfig</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>LevelConfig</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>LevelConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Level.TbLevelStageConfig</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>LevelStageConfig</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>LevelStageConfig.xlsx</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="5.91666666666667" customWidth="1" style="4" min="1" max="1"/>
@@ -1363,36 +1363,21 @@
         </is>
       </c>
       <c r="D12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
           <t>LevelConfig.xlsx</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>Level.TbLevelStageConfig</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>LevelStageConfig</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>LevelStageConfig.xlsx</t>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>LevelId</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="5.91666666666667" customWidth="1" style="4" min="1" max="1"/>
@@ -1278,11 +1278,21 @@
         </is>
       </c>
       <c r="D8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
           <t>MonsterConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1380,7 @@
           <t>LevelConfig.xlsx</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>LevelId</t>
         </is>
@@ -1378,6 +1388,61 @@
       <c r="G12" s="0" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hero.TbHeroGrowthConfig</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HeroGrowthConfig</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HeroGrowthConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HeroId+Level</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Profile.TbProfileConfig</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ProfileConfig</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ProfileConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="5.91666666666667" customWidth="1" style="4" min="1" max="1"/>
@@ -1285,12 +1285,12 @@
           <t>MonsterConfig.xlsx</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
@@ -1392,55 +1392,80 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Hero.TbHeroGrowthConfig</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>HeroGrowthConfig</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>HeroGrowthConfig.xlsx</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>HeroId+Level</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Profile.TbProfileConfig</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>ProfileConfig</t>
         </is>
       </c>
-      <c r="D14" t="b">
+      <c r="D14" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>ProfileConfig.xlsx</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Loot.TbDropConfig</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DropConfig</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DropConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>one</t>
         </is>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1,177 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68025920e61b47a3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="20">
     <font>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <sz val="11"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <i val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="等线"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -179,193 +156,161 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
@@ -406,7 +351,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,73 +570,80 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="22" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -761,6 +713,23 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -885,23 +854,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -911,23 +880,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -935,26 +904,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -989,17 +955,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1014,447 +980,441 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="5.91666666666667" customWidth="1" style="4" min="1" max="1"/>
-    <col width="29" customWidth="1" style="4" min="2" max="2"/>
-    <col width="19.0833333333333" customWidth="1" style="4" min="3" max="3"/>
-    <col width="53.0833333333333" customWidth="1" style="4" min="4" max="4"/>
-    <col width="22.6666666666667" customWidth="1" style="4" min="5" max="5"/>
-    <col width="89.25" customWidth="1" style="4" min="6" max="6"/>
-    <col width="31.5" customWidth="1" style="4" min="7" max="7"/>
-    <col width="56.75" customWidth="1" style="4" min="8" max="8"/>
-    <col width="9" customWidth="1" style="4" min="9" max="9"/>
-    <col width="4.75" customWidth="1" style="4" min="10" max="10"/>
-    <col width="33" customWidth="1" style="4" min="11" max="11"/>
+    <col min="1" max="1" width="5.916666507720947" style="4" customWidth="1"/>
+    <col min="2" max="2" width="29" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.08333396911621" style="4" customWidth="1"/>
+    <col min="4" max="4" width="53.08333206176758" style="4" customWidth="1"/>
+    <col min="5" max="5" width="22.66666603088379" style="4" customWidth="1"/>
+    <col min="6" max="6" width="89.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="31.5" style="4" customWidth="1"/>
+    <col min="8" max="8" width="56.75" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9" style="4" customWidth="1"/>
+    <col min="10" max="10" width="4.75" style="4" customWidth="1"/>
+    <col min="11" max="11" width="33" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t xml:space="preserve">full_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>value_type</t>
+          <t xml:space="preserve">value_type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>read_schema_from_file</t>
+          <t xml:space="preserve">read_schema_from_file</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>input</t>
+          <t xml:space="preserve">input</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t xml:space="preserve">index</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t xml:space="preserve">mode</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>group</t>
+          <t xml:space="preserve">group</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t xml:space="preserve">comment</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t xml:space="preserve">tags</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="1">
+          <t xml:space="preserve">output</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>全名(包含模块和名字)</t>
+          <t xml:space="preserve">全名(包含模块和名字)</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>记录类名</t>
+          <t xml:space="preserve">记录类名</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>从excel读取定义</t>
+          <t xml:space="preserve">从excel读取定义</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>文件列表</t>
+          <t xml:space="preserve">文件列表</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>表id字段</t>
+          <t xml:space="preserve">表id字段</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>模式</t>
+          <t xml:space="preserve">模式</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>分组</t>
+          <t xml:space="preserve">分组</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>注释</t>
+          <t xml:space="preserve">注释</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>输出文件名</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="1">
+          <t xml:space="preserve">输出文件名</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+          <t xml:space="preserve">false时取已有定义，true为从excel标题头和属性栏读取定义</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>可以多个，以逗号','分隔</t>
+          <t xml:space="preserve">可以多个，以逗号','分隔</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+          <t xml:space="preserve">为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>取值one|map|list，为空自动为map</t>
+          <t xml:space="preserve">取值one|map|list，为空自动为map</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+          <t xml:space="preserve">取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>UI.TbUIFormConfig</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>UIFormConfig</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="b">
+          <t xml:space="preserve">默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI.TbUIFormConfig</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIFormConfig</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>界面UI.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="3">
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>Entity.TbEntityConfig</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>EntityConfig</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="b">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">界面UI.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entity.TbEntityConfig</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EntityConfig</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>实体.xlsx</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">实体.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>Hero.TbHeroConfig</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>HeroConfig</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="b">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hero.TbHeroConfig</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeroConfig</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>HeroConfig.xlsx</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeroConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>Hero.TbHeroLevelConfig</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>HeroLevelConfig</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="b">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hero.TbHeroLevelConfig</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeroLevelConfig</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>HeroLevelConfig.xlsx</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeroLevelConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>Monster.TbMonsterConfig</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>MonsterConfig</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="b">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monster.TbMonsterConfig</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MonsterConfig</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>MonsterConfig.xlsx</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MonsterConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">map</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>Battle.TbAttackConfig</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>AttackConfig</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="b">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Battle.TbAttackConfig</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackConfig</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>AttackConfig.xlsx</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AttackConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>Battle.TbBattleConfig</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>BattleConfig</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="b">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Battle.TbBattleConfig</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BattleConfig</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>BattleConfig.xlsx</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>one</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BattleConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>Sound.TbSoundConfig</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>SoundConfig</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="b">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sound.TbSoundConfig</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoundConfig</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>SoundConfig.xlsx</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoundConfig.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>Level.TbLevelConfig</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>LevelConfig</t>
-        </is>
-      </c>
-      <c r="D12" s="0" t="b">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level.TbLevelConfig</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LevelConfig</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>LevelConfig.xlsx</t>
-        </is>
-      </c>
-      <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t>LevelId</t>
-        </is>
-      </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LevelConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LevelId</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">map</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>Hero.TbHeroGrowthConfig</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>HeroGrowthConfig</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="b">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hero.TbHeroGrowthConfig</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeroGrowthConfig</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>HeroGrowthConfig.xlsx</t>
-        </is>
-      </c>
-      <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t>HeroId+Level</t>
-        </is>
-      </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeroGrowthConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeroId+Level</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">list</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>Profile.TbProfileConfig</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>ProfileConfig</t>
-        </is>
-      </c>
-      <c r="D14" s="0" t="b">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Profile.TbProfileConfig</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ProfileConfig</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>ProfileConfig.xlsx</t>
-        </is>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>one</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ProfileConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loot.TbDropConfig</t>
+          <t xml:space="preserve">Loot.TbDropConfig</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DropConfig</t>
+          <t xml:space="preserve">DropConfig</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -1462,17 +1422,97 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DropConfig.xlsx</t>
+          <t xml:space="preserve">DropConfig.xlsx</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>one</t>
-        </is>
-      </c>
+          <t xml:space="preserve">one</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16" t="str">
+        <v>Equipment.TbEquipmentConfig</v>
+      </c>
+      <c r="C16" t="str">
+        <v>EquipmentConfig</v>
+      </c>
+      <c r="D16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="str">
+        <v>EquipmentConfig.xlsx</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Id</v>
+      </c>
+      <c r="G16" t="str">
+        <v>map</v>
+      </c>
+      <c r="H16"/>
+      <c r="I16" t="str">
+        <v>造一粗糙与普通装备</v>
+      </c>
+      <c r="J16"/>
+      <c r="K16"/>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17" t="str">
+        <v>Loot.TbEquipmentDropPoolConfig</v>
+      </c>
+      <c r="C17" t="str">
+        <v>EquipmentDropPoolConfig</v>
+      </c>
+      <c r="D17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="str">
+        <v>EquipmentDropPoolConfig.xlsx</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Id</v>
+      </c>
+      <c r="G17" t="str">
+        <v>map</v>
+      </c>
+      <c r="H17"/>
+      <c r="I17" t="str">
+        <v>怪物装备池</v>
+      </c>
+      <c r="J17"/>
+      <c r="K17"/>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18" t="str">
+        <v>Loot.TbPickupConfig</v>
+      </c>
+      <c r="C18" t="str">
+        <v>PickupConfig</v>
+      </c>
+      <c r="D18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
+        <v>PickupConfig.xlsx</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Id</v>
+      </c>
+      <c r="G18" t="str">
+        <v>map</v>
+      </c>
+      <c r="H18"/>
+      <c r="I18" t="str">
+        <v>地面恢复品，接触立即使用</v>
+      </c>
+      <c r="J18"/>
+      <c r="K18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68025920e61b47a3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf27f414ee177430b"/>
   </sheets>
 </workbook>
 </file>
@@ -1512,6 +1512,168 @@
       <c r="J18"/>
       <c r="K18"/>
     </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19" t="str">
+        <v>Skills.TbSkillConfig</v>
+      </c>
+      <c r="C19" t="str">
+        <v>SkillConfig</v>
+      </c>
+      <c r="D19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>SkillConfig.xlsx</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Id</v>
+      </c>
+      <c r="G19" t="str">
+        <v>map</v>
+      </c>
+      <c r="H19"/>
+      <c r="I19" t="str">
+        <v>造一主动技能面板、学习费用与耗蓝</v>
+      </c>
+      <c r="J19"/>
+      <c r="K19"/>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20" t="str">
+        <v>Skills.TbPassiveConfig</v>
+      </c>
+      <c r="C20" t="str">
+        <v>PassiveConfig</v>
+      </c>
+      <c r="D20" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>PassiveConfig.xlsx</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PassiveId+Level</v>
+      </c>
+      <c r="G20" t="str">
+        <v>list</v>
+      </c>
+      <c r="H20"/>
+      <c r="I20" t="str">
+        <v>造一五项被动，每项五级</v>
+      </c>
+      <c r="J20"/>
+      <c r="K20"/>
+    </row>
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21" t="str">
+        <v>Skills.TbSkillHitConfig</v>
+      </c>
+      <c r="C21" t="str">
+        <v>SkillHitConfig</v>
+      </c>
+      <c r="D21" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="str">
+        <v>SkillHitConfig.xlsx</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Id</v>
+      </c>
+      <c r="G21" t="str">
+        <v>map</v>
+      </c>
+      <c r="H21"/>
+      <c r="I21" t="str">
+        <v>技能分段威力、伤害类型、击退与总命中预算</v>
+      </c>
+      <c r="J21"/>
+      <c r="K21"/>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22" t="str">
+        <v>Skills.TbSkillActionConfig</v>
+      </c>
+      <c r="C22" t="str">
+        <v>SkillActionConfig</v>
+      </c>
+      <c r="D22" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="str">
+        <v>SkillActionConfig.xlsx</v>
+      </c>
+      <c r="F22" t="str">
+        <v>SkillId</v>
+      </c>
+      <c r="G22" t="str">
+        <v>map</v>
+      </c>
+      <c r="H22"/>
+      <c r="I22" t="str">
+        <v>已准备的悟空动作资源、起手音与无敌时间</v>
+      </c>
+      <c r="J22"/>
+      <c r="K22"/>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23" t="str">
+        <v>Skills.TbSkillEffectConfig</v>
+      </c>
+      <c r="C23" t="str">
+        <v>SkillEffectConfig</v>
+      </c>
+      <c r="D23" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="str">
+        <v>SkillEffectConfig.xlsx</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Id</v>
+      </c>
+      <c r="G23" t="str">
+        <v>map</v>
+      </c>
+      <c r="H23"/>
+      <c r="I23" t="str">
+        <v>悟空独立特效、分段声音与普通/无双缩放</v>
+      </c>
+      <c r="J23"/>
+      <c r="K23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24" t="str">
+        <v>Skills.TbSkillTimelineConfig</v>
+      </c>
+      <c r="C24" t="str">
+        <v>SkillTimelineConfig</v>
+      </c>
+      <c r="D24" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="str">
+        <v>SkillTimelineConfig.xlsx</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Id</v>
+      </c>
+      <c r="G24" t="str">
+        <v>map</v>
+      </c>
+      <c r="H24"/>
+      <c r="I24" t="str">
+        <v>悟空技能秒制位移、分段编号、特效及条件分支</v>
+      </c>
+      <c r="J24"/>
+      <c r="K24"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a0d97cec8124680"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rddf82793b44d4cf6"/>
   </sheets>
 </workbook>
 </file>
@@ -308,20 +308,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <col min="1" max="1" width="5.916666507720947" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="29" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="19.08333396911621" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="53.08333206176758" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.66666603088379" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="89.25" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="31.5" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="40" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="44" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="56.75" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="9" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="4.75" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="33" hidden="0" customWidth="1"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="14" customHeight="1">
       <c r="A1" s="1" t="str">
         <v>##var</v>
@@ -385,7 +385,6 @@
       <c r="I2" s="1" t="str">
         <v>注释</v>
       </c>
-      <c r="J2" s="1"/>
       <c r="K2" s="1" t="str">
         <v>输出文件名</v>
       </c>
@@ -394,8 +393,6 @@
       <c r="A3" s="1" t="str">
         <v>##</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
       <c r="D3" s="1" t="str">
         <v>false时取已有定义，true为从excel标题头和属性栏读取定义</v>
       </c>
@@ -411,14 +408,11 @@
       <c r="H3" s="1" t="str">
         <v>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
       <c r="K3" s="1" t="str">
         <v>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</v>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="2"/>
       <c r="B4" s="3" t="str">
         <v>UI.TbUIFormConfig</v>
       </c>
@@ -431,15 +425,8 @@
       <c r="E4" s="3" t="str">
         <v>UIFormConfig@Resources.xlsx</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="4"/>
       <c r="B5" s="3" t="str">
         <v>Entity.TbEntityConfig</v>
       </c>
@@ -452,15 +439,8 @@
       <c r="E5" s="3" t="str">
         <v>EntityConfig@Resources.xlsx</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="5"/>
       <c r="B6" s="3" t="str">
         <v>Hero.TbHeroConfig</v>
       </c>
@@ -473,15 +453,8 @@
       <c r="E6" s="3" t="str">
         <v>HeroConfig@Hero.xlsx</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="5"/>
       <c r="B7" s="3" t="str">
         <v>Hero.TbHeroLevelConfig</v>
       </c>
@@ -494,15 +467,8 @@
       <c r="E7" s="3" t="str">
         <v>HeroLevelConfig@Hero.xlsx</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="5"/>
       <c r="B8" s="3" t="str">
         <v>Monster.TbMonsterConfig</v>
       </c>
@@ -513,7 +479,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="str">
-        <v>MonsterConfig@Enemy.xlsx</v>
+        <v>MonsterConfig@Enemy.xlsx,BossConfig@Enemy.xlsx</v>
       </c>
       <c r="F8" s="3" t="str">
         <v>Id</v>
@@ -521,13 +487,8 @@
       <c r="G8" s="3" t="str">
         <v>map</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="5"/>
       <c r="B9" s="3" t="str">
         <v>Battle.TbAttackConfig</v>
       </c>
@@ -540,15 +501,8 @@
       <c r="E9" s="3" t="str">
         <v>AttackConfig@Combat.xlsx</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="5"/>
       <c r="B10" s="3" t="str">
         <v>Battle.TbBattleConfig</v>
       </c>
@@ -561,17 +515,11 @@
       <c r="E10" s="3" t="str">
         <v>BattleConfig@Combat.xlsx</v>
       </c>
-      <c r="F10" s="5"/>
       <c r="G10" s="3" t="str">
         <v>one</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="5"/>
       <c r="B11" s="3" t="str">
         <v>Sound.TbSoundConfig</v>
       </c>
@@ -584,15 +532,8 @@
       <c r="E11" s="3" t="str">
         <v>SoundConfig@Resources.xlsx</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="5"/>
       <c r="B12" s="3" t="str">
         <v>Level.TbLevelConfig</v>
       </c>
@@ -611,13 +552,8 @@
       <c r="G12" s="3" t="str">
         <v>map</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="5"/>
       <c r="B13" s="3" t="str">
         <v>Hero.TbHeroGrowthConfig</v>
       </c>
@@ -631,18 +567,13 @@
         <v>HeroGrowthConfig@Hero.xlsx</v>
       </c>
       <c r="F13" s="3" t="str">
-        <v>HeroId+Level</v>
+        <v>HeroId</v>
       </c>
       <c r="G13" s="3" t="str">
-        <v>list</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+        <v>map</v>
+      </c>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="5"/>
       <c r="B14" s="3" t="str">
         <v>Profile.TbProfileConfig</v>
       </c>
@@ -655,17 +586,11 @@
       <c r="E14" s="3" t="str">
         <v>ProfileConfig.xlsx</v>
       </c>
-      <c r="F14" s="5"/>
       <c r="G14" s="3" t="str">
         <v>one</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="3"/>
       <c r="B15" s="3" t="str">
         <v>Equipment.TbEquipmentConfig</v>
       </c>
@@ -684,15 +609,11 @@
       <c r="G15" s="3" t="str">
         <v>map</v>
       </c>
-      <c r="H15" s="3"/>
       <c r="I15" s="3" t="str">
         <v>造一粗糙与普通装备</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
     </row>
     <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="3"/>
       <c r="B16" s="3" t="str">
         <v>Loot.TbEquipmentDropPoolConfig</v>
       </c>
@@ -711,15 +632,11 @@
       <c r="G16" s="3" t="str">
         <v>map</v>
       </c>
-      <c r="H16" s="3"/>
       <c r="I16" s="3" t="str">
         <v>怪物装备池</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="3"/>
       <c r="B17" s="3" t="str">
         <v>Loot.TbPickupConfig</v>
       </c>
@@ -738,15 +655,11 @@
       <c r="G17" s="3" t="str">
         <v>map</v>
       </c>
-      <c r="H17" s="3"/>
       <c r="I17" s="3" t="str">
         <v>地面恢复品，接触立即使用</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="3"/>
       <c r="B18" s="3" t="str">
         <v>Skills.TbSkillConfig</v>
       </c>
@@ -765,15 +678,11 @@
       <c r="G18" s="3" t="str">
         <v>map</v>
       </c>
-      <c r="H18" s="3"/>
       <c r="I18" s="3" t="str">
         <v>造一主动技能面板、学习费用与耗蓝</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
     </row>
     <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="3"/>
       <c r="B19" s="3" t="str">
         <v>Skills.TbPassiveConfig</v>
       </c>
@@ -781,23 +690,20 @@
         <v>PassiveConfig</v>
       </c>
       <c r="D19" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>PassiveConfig@Skills.xlsx</v>
       </c>
       <c r="F19" s="3" t="str">
-        <v>PassiveId+Level</v>
+        <v>PassiveId</v>
       </c>
       <c r="G19" s="3" t="str">
-        <v>list</v>
-      </c>
-      <c r="H19" s="3"/>
+        <v>map</v>
+      </c>
       <c r="I19" s="3" t="str">
         <v>造一五项被动，每项五级</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
